--- a/record.xlsx
+++ b/record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo T14\Documents\Dormitory\Water Collection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo T14\Documents\Dormitory\Water Collection Management System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A17FE2-45E4-4394-B22D-7E5D4505F0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7333A97-5E7D-4214-B33C-9740A02BA3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="12090" tabRatio="683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="occupants" sheetId="14" r:id="rId1"/>
@@ -1203,7 +1203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1281,9 +1281,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -5114,7 +5111,7 @@
       <c r="D150" s="1"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="31">
+      <c r="G150" s="27">
         <v>1</v>
       </c>
       <c r="H150" s="1" t="s">
@@ -5131,10 +5128,10 @@
       <c r="D151" s="1"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="31">
+      <c r="G151" s="27">
         <v>2</v>
       </c>
-      <c r="H151" s="32">
+      <c r="H151" s="31">
         <v>46248</v>
       </c>
       <c r="I151">
@@ -5148,10 +5145,10 @@
       <c r="D152" s="1"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="31">
+      <c r="G152" s="27">
         <v>3</v>
       </c>
-      <c r="H152" s="33">
+      <c r="H152" s="32">
         <v>46252</v>
       </c>
       <c r="I152">
@@ -5165,10 +5162,10 @@
       <c r="D153" s="1"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="31">
+      <c r="G153" s="27">
         <v>4</v>
       </c>
-      <c r="H153" s="32">
+      <c r="H153" s="31">
         <v>46253</v>
       </c>
       <c r="I153">
@@ -5182,10 +5179,10 @@
       <c r="D154" s="1"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
-      <c r="G154" s="31">
+      <c r="G154" s="27">
         <v>5</v>
       </c>
-      <c r="H154" s="32">
+      <c r="H154" s="31">
         <v>46254</v>
       </c>
       <c r="I154">
@@ -5199,10 +5196,10 @@
       <c r="D155" s="1"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
-      <c r="G155" s="31">
+      <c r="G155" s="27">
         <v>6</v>
       </c>
-      <c r="H155" s="32">
+      <c r="H155" s="31">
         <v>46260</v>
       </c>
       <c r="I155">
@@ -5216,10 +5213,10 @@
       <c r="D156" s="1"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
-      <c r="G156" s="31">
+      <c r="G156" s="27">
         <v>7</v>
       </c>
-      <c r="H156" s="32">
+      <c r="H156" s="31">
         <v>46263</v>
       </c>
       <c r="I156">
@@ -5233,10 +5230,10 @@
       <c r="D157" s="1"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
-      <c r="G157" s="31">
+      <c r="G157" s="27">
         <v>8</v>
       </c>
-      <c r="H157" s="32">
+      <c r="H157" s="31">
         <v>46266</v>
       </c>
       <c r="I157">
